--- a/entregables_planta/Matriz_Decision_Retrabajo_Piso.xlsx
+++ b/entregables_planta/Matriz_Decision_Retrabajo_Piso.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semaforo_Decision_Piso" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OPL_Criterios_Calidad_Piso" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen_Ejecutivo_COPQ" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,12 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="$#,##0.00"/>
-    <numFmt numFmtId="166" formatCode="+$#,##0.00;-$#,##0.00;$0.00"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,23 +32,68 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="001B365D"/>
-      <sz val="16"/>
+      <sz val="15"/>
     </font>
     <font>
       <name val="Calibri"/>
       <i val="1"/>
       <color rgb="00475467"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00842029"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00842029"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="12"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00842029"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000F5132"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
       <sz val="11"/>
     </font>
     <font>
@@ -61,36 +105,11 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
       <color rgb="000F5132"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
       <sz val="11"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <sz val="9"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -99,14 +118,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001B365D"/>
-        <bgColor rgb="001B365D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8F4FD"/>
-        <bgColor rgb="00E8F4FD"/>
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
     <fill>
@@ -123,18 +136,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
+        <fgColor rgb="001B365D"/>
+        <bgColor rgb="001B365D"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -156,55 +169,11 @@
         <color rgb="00D0D5DD"/>
       </bottom>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00D0D5DD"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00D0D5DD"/>
-      </right>
-      <top style="thin">
-        <color rgb="00D0D5DD"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00D0D5DD"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00D0D5DD"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00D0D5DD"/>
-      </right>
-      <top style="thin">
-        <color rgb="00D0D5DD"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00D0D5DD"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -215,44 +184,61 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -620,377 +606,564 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H20"/>
+  <dimension ref="A2:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>HERRAMIENTA DE DECISIÓN EN PISO: SEMÁFORO RETRABAJO VS. SCRAP</t>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>LECCIÓN DE UN PUNTO (OPL) | ESTÁNDAR VISUAL DE CALIDAD EN PISO</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Aseguramiento de Calidad &amp; Control de Costos (COPQ) | Ing. Angelo Apolo</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Código: OPL-CAL-003 | Revisión: 02 | Aprobado: Ing. Angelo Apolo (Jefe QA/QC &amp; Black Belt) | Líneas A &amp; B</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>1. PARÁMETROS DE INSPECCIÓN EN LÍNEA</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>2. RECOMENDACIÓN OPERATIVA (SEMÁFORO)</t>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>⚠️ REGLA DE ORO DE PLANTA: PROHIBIDO RETRABAJAR DEFECTOS EN SEVERIDAD 3 (GRIETAS O DEFORMACIONES CRÍTICAS)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Tipo de Defecto:</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>Grieta / Fisura</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>Opciones: Dimensión / Acabado / Grieta / Rayón / Contaminación</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Probabilidad Estimada de Éxito:</t>
-        </is>
-      </c>
-      <c r="G6" s="7">
-        <f>MAX(0.05, MIN(0.98, 1.15 - (C7*0.24) - (C9*0.012) - ((C10-100)*0.0015) + IF(C8="Visión Artificial", 0.05, IF(C8="Sensor", 0.02, 0))))</f>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Más del 50% de las piezas graves fracasan en reproceso. Retrabajar cuesta $126.78 USD vs. $101.31 USD de Scrap directo. ¡Toda pieza severa va a Gaveta Roja!</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Tipo de Defecto</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Severidad 1 (Leve)
+🟢 GAVETA VERDE: REPROCESO</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Severidad 2 (Moderada)
+🟡 GAVETA AMARILLA: EVALUAR</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Severidad 3 (Crítica / Estructural)
+🔴 GAVETA ROJA: SCRAP DIRECTO</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Criterio Físico / Tolerancia</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Acción Inmediata en Línea</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Ahorro Evitado</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Grieta / Fisura
+(crack)</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Microfisura capilar no pasante (&lt;2 mm).
+Éxito histórico: 82%</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Fisura superficial (2 - 5 mm).
+Autorizado solo con máquina &lt;6 años.
+Éxito histórico: 58%</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Fisura pasante o ramificada (&gt;5 mm).
+Éxito: &lt;38% (Fracaso garantizado).</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>Inspección con lupa 10x y líquido penetrante.</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>Marcar con pintura roja indeleble y depositar en contenedor de Scrap.</t>
+        </is>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>+$25.47 USD / pieza</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Desviación Dimensional
+(dimension)</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Desvío menor respecto a cota (±0.05 mm).
+Éxito histórico: 88%</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Desvío moderado (±0.10 a 0.25 mm).
+Requiere verificación de espesor de pared.
+Éxito histórico: 76%</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>Desvío crítico (&gt;0.30 mm) o falta de material.
+Imposible recuperar tolerancia.</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>Medición con micrómetro digital / galga pasa-no pasa.</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>Ajuste de mordazas de máquina y verificación de setpoint.</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>+$25.47 USD / pieza</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Acabado Superficial
+(finish)</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Rebaba menor o marca de enfriamiento.
+Éxito histórico: 87%</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Textura irregular o mancha no penetrante.
+Autorizado si no afecta cara de ensamble.
+Éxito histórico: 72%</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Porosidad abierta o desgarre térmico.
+Defecto penetra &gt;20% del espesor de pared.</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>Comparación contra muestra patrón de rugosidad.</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>Desbarbado manual en banco auxiliar (máximo 10 min).</t>
+        </is>
+      </c>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>+$25.47 USD / pieza</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Rayón / Abrasión
+(scratch)</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Rayón leve que no traba la uña (&lt;0.05 mm).
+Éxito histórico: 85%</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Rayón visible (0.05 - 0.15 mm).
+Evaluar si compromete estanqueidad o sello.
+Éxito histórico: 62%</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>Surco profundo (&gt;0.20 mm) o daño en junta.
+Riesgo crítico de reclamo a cliente.</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>Inspección visual bajo luz halógena estandarizada.</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>Pulido abrasivo solo en caras no funcionales.</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>+$25.47 USD / pieza</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Contaminación
+(contamination)</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Partículas secas de polvo superficial.
+Éxito histórico: 86%</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Mancha de lubricante o grasa lavable.
+Requiere desengrase ultrasónico controlado.
+Éxito histórico: 65%</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>Inclusiones fundidas o viruta metálica incrustada.
+Falla estructural irreparable.</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>Verificación con hisopado e inspección óptica.</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>Limpieza neumática en estación de soplado.</t>
+        </is>
+      </c>
+      <c r="G13" s="11" t="inlineStr">
+        <is>
+          <t>+$25.47 USD / pieza</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A5:G5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A2:F18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>CUADRO EJECUTIVO: COSTO DE NO CALIDAD (COPQ) Y RETORNO FINANCIERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>Auditoría de 10,000 Eventos de Producción | Ahorro a Capex Cero por Optimización de Decisiones de Calidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>1. MATRIZ DE COSTO UNITARIO SEGÚN DESENLACE OPERATIVO</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>Desenlace Operativo</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>Eventos en Muestra</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>Costo Medio USD</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>Costo Total USD</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>Comportamiento en Planta</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>1. Aprobado Directo</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="n">
+        <v>6728</v>
+      </c>
+      <c r="C7" s="17" t="n">
+        <v>23.54</v>
+      </c>
+      <c r="D7" s="17">
+        <f>B7*C7</f>
         <v/>
       </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Severidad del Defecto (1 a 3):</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>1 = Leve | 2 = Moderado | 3 = Crítico/Estructural</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>DICTAMEN EN PISO:</t>
-        </is>
-      </c>
-      <c r="G7" s="9">
-        <f>IF(C7=3, "🔴 SCRAP DIRECTO", IF(G6&gt;=0.75, "🟢 RETRABAJAR", IF(G6&gt;=0.55, "🟡 EVALUAR SUPERVISOR", "🔴 SCRAP DIRECTO")))</f>
+      <c r="E7" s="18" t="inlineStr">
+        <is>
+          <t>Flujo de calidad conforme a primera pasada (Right First Time).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>2. Retrabajo Exitoso</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="n">
+        <v>2033</v>
+      </c>
+      <c r="C8" s="17" t="n">
+        <v>36.67</v>
+      </c>
+      <c r="D8" s="17">
+        <f>B8*C8</f>
         <v/>
       </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Método de Inspección:</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Visión Artificial</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Manual / Sensor / Visión Artificial</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="n"/>
+      <c r="E8" s="18" t="inlineStr">
+        <is>
+          <t>Recuperación económica rentable en banco auxiliar.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Antigüedad de Máquina (años):</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>Promedio planta: 6.0 años</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>Costo Esperado si se Retrabaja:</t>
-        </is>
-      </c>
-      <c r="G9" s="11">
-        <f>(G6*36.67) + ((1-G6)*126.78)</f>
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>3. Scrap Directo</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="n">
+        <v>57</v>
+      </c>
+      <c r="C9" s="17" t="n">
+        <v>101.31</v>
+      </c>
+      <c r="D9" s="17">
+        <f>B9*C9</f>
         <v/>
       </c>
+      <c r="E9" s="18" t="inlineStr">
+        <is>
+          <t>Pérdida de material contenida inmediatamente.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Velocidad de Operación (u/h):</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>125</v>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>Nominal: 115 u/h (Forzada: &gt;135 u/h)</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>Costo si se envía a Scrap Directo:</t>
-        </is>
-      </c>
-      <c r="G10" s="11" t="n">
-        <v>101.31</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Grado de Materia Prima:</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Grado B</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>Grado A (Premium) / Grado B / Grado C</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>Beneficio Neto de la Decisión:</t>
-        </is>
-      </c>
-      <c r="G11" s="12">
-        <f>IF(LEFT(G7,1)="🔴", 126.78 - 101.31, 101.31 - G9)</f>
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>4. Retrabajo Fallido (Scrap)</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="n">
+        <v>191</v>
+      </c>
+      <c r="C10" s="21" t="n">
+        <v>126.78</v>
+      </c>
+      <c r="D10" s="21">
+        <f>B10*C10</f>
         <v/>
       </c>
+      <c r="E10" s="18" t="inlineStr">
+        <is>
+          <t>PÉRDIDA DOBLE: Material destruido + mano de obra + energía.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>2. CUANTIFICACIÓN DEL IMPACTO FINANCIERO AHORRADO</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>3. TABLA GUÍA RÁPIDA DE DECISIÓN SEGÚN SEVERIDAD Y DEFECTO</t>
-        </is>
-      </c>
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>Piezas en Scrap Doble Costo Erradicadas:</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="n">
+        <v>191</v>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>Unidades severas no reprocesadas</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="n"/>
+      <c r="E14" s="24" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="13" t="inlineStr">
-        <is>
-          <t>Tipo de Defecto</t>
-        </is>
-      </c>
-      <c r="C15" s="13" t="inlineStr">
-        <is>
-          <t>Severidad 1 (Leve)</t>
-        </is>
-      </c>
-      <c r="D15" s="13" t="inlineStr">
-        <is>
-          <t>Severidad 2 (Moderado)</t>
-        </is>
-      </c>
-      <c r="E15" s="13" t="inlineStr">
-        <is>
-          <t>Severidad 3 (Grave/Estructural)</t>
-        </is>
-      </c>
-      <c r="F15" s="13" t="inlineStr">
-        <is>
-          <t>Regla Operativa de Planta</t>
-        </is>
-      </c>
-      <c r="G15" s="14" t="n"/>
-      <c r="H15" s="15" t="n"/>
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>Sobrecosto Evitado por Unidad:</t>
+        </is>
+      </c>
+      <c r="B15" s="25" t="n">
+        <v>25.47</v>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>Diferencia ($126.78 - $101.31 USD)</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="n"/>
+      <c r="E15" s="24" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Dimensión / Tolerancia</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>🟢 Retrabajar (88% éxito)</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>🟢 Retrabajar (76% éxito)</t>
-        </is>
-      </c>
-      <c r="E16" s="17" t="inlineStr">
-        <is>
-          <t>🔴 Scrap Directo (&lt;48%)</t>
-        </is>
-      </c>
-      <c r="F16" s="18" t="inlineStr">
-        <is>
-          <t>Ajuste de mordazas y calibración en línea.</t>
-        </is>
-      </c>
-      <c r="H16" s="10" t="n"/>
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Ahorro Neto Auditado en Muestra (10k eventos):</t>
+        </is>
+      </c>
+      <c r="B16" s="26">
+        <f>B14*B15</f>
+        <v/>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>Ahorro directo inmediato</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="n"/>
+      <c r="E16" s="24" t="n"/>
     </row>
     <row r="17">
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Acabado Superficial</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>🟢 Retrabajar (87% éxito)</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>🟢 Retrabajar (72% éxito)</t>
-        </is>
-      </c>
-      <c r="E17" s="17" t="inlineStr">
-        <is>
-          <t>🔴 Scrap Directo (&lt;48%)</t>
-        </is>
-      </c>
-      <c r="F17" s="18" t="inlineStr">
-        <is>
-          <t>Pulido o reacondicionado térmico permitido.</t>
-        </is>
-      </c>
-      <c r="H17" s="10" t="n"/>
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>Horas Hombre Productivas Recuperadas:</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="n">
+        <v>78</v>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>Horas de operario devueltas a línea</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="n"/>
+      <c r="E17" s="24" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Contaminación</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>🟢 Retrabajar (86% éxito)</t>
-        </is>
-      </c>
-      <c r="D18" s="19" t="inlineStr">
-        <is>
-          <t>🟡 Evaluar (65% éxito)</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="inlineStr">
-        <is>
-          <t>🔴 Scrap Directo (&lt;45%)</t>
-        </is>
-      </c>
-      <c r="F18" s="18" t="inlineStr">
-        <is>
-          <t>Limpieza solo si no penetra matriz del material.</t>
-        </is>
-      </c>
-      <c r="H18" s="10" t="n"/>
-    </row>
-    <row r="19">
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Rayón Profundo</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>🟢 Retrabajar (85% éxito)</t>
-        </is>
-      </c>
-      <c r="D19" s="19" t="inlineStr">
-        <is>
-          <t>🟡 Evaluar (62% éxito)</t>
-        </is>
-      </c>
-      <c r="E19" s="17" t="inlineStr">
-        <is>
-          <t>🔴 Scrap Directo (&lt;42%)</t>
-        </is>
-      </c>
-      <c r="F19" s="18" t="inlineStr">
-        <is>
-          <t>Inspección de guías mecánicas y rodillos.</t>
-        </is>
-      </c>
-      <c r="H19" s="10" t="n"/>
-    </row>
-    <row r="20">
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Grieta / Fisura</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>🟢 Retrabajar (82% éxito)</t>
-        </is>
-      </c>
-      <c r="D20" s="19" t="inlineStr">
-        <is>
-          <t>🟡 Evaluar (58% éxito)</t>
-        </is>
-      </c>
-      <c r="E20" s="17" t="inlineStr">
-        <is>
-          <t>🔴 Scrap Directo (&lt;38%)</t>
-        </is>
-      </c>
-      <c r="F20" s="18" t="inlineStr">
-        <is>
-          <t>PÉRDIDA ESTRUCTURAL: Riesgo crítico de escape a cliente.</t>
-        </is>
-      </c>
-      <c r="H20" s="10" t="n"/>
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>Ahorro Anualizado Proyectado (100k eventos/año):</t>
+        </is>
+      </c>
+      <c r="B18" s="26">
+        <f>B16*10</f>
+        <v/>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>Impacto EBITDA anual a Capex Cero</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="n"/>
+      <c r="E18" s="24" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="B14:H14"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="G7:H8"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="F15:H15"/>
+  <mergeCells count="9">
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="C15:E15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
